--- a/IngSoftware/propuesta/Riesgos/MissTortas-TemplateRiesgos.xlsx
+++ b/IngSoftware/propuesta/Riesgos/MissTortas-TemplateRiesgos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rojas\source\repos\TrabajoFinalAUS\IngSoftware\propuesta\Riesgos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D628D957-907A-434D-B857-99079CA71A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D09BA58A-A918-4B87-825C-34171F74DF99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -136,9 +136,6 @@
     <t>29/8/2026</t>
   </si>
   <si>
-    <t>Dado que los repositorios de codigo ofrecidos por compañías pueden ser inaccesibes (por caídas de sus servicios, falta de acceso a la internet), existe la posibilidad de que los desarrolladores no puedan colaborar realizando revisiones de codigo</t>
-  </si>
-  <si>
     <t>Dado que el proyecto puede tardar demasiado tiempo, existe la posibilidad de que el cliente pueda encontrar otras soluciones y el software desarrollado pierda su ventana de mercado, discontinuando el proyecto.</t>
   </si>
   <si>
@@ -228,6 +225,9 @@
   </si>
   <si>
     <t>Asignar como fondo de contingencia la exposicion al riesgo que representa.</t>
+  </si>
+  <si>
+    <t>Dado que los repositorios de codigo ofrecidos por compañías pueden ser inaccesibes (por caídas de sus servicios, falta de acceso a la internet), existe la posibilidad de que los desarrolladores no puedan colaborar realizando revisiones de codigo (Pull Request).</t>
   </si>
 </sst>
 </file>
@@ -459,7 +459,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -511,25 +511,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -541,17 +526,14 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -562,7 +544,10 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -595,13 +580,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -611,22 +589,11 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="Arial"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -763,13 +730,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -779,6 +739,31 @@
         <top style="thin">
           <color indexed="64"/>
         </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -854,29 +839,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B781CC50-6B6D-4940-87E7-D9142166446E}" name="Tabla1" displayName="Tabla1" ref="A3:H12" totalsRowShown="0" dataDxfId="4" headerRowBorderDxfId="13" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B781CC50-6B6D-4940-87E7-D9142166446E}" name="Tabla1" displayName="Tabla1" ref="A3:H12" totalsRowShown="0" dataDxfId="13" headerRowBorderDxfId="14" tableBorderDxfId="12">
   <autoFilter ref="A3:H12" xr:uid="{B781CC50-6B6D-4940-87E7-D9142166446E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H12">
     <sortCondition descending="1" ref="G3:G12"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4304278C-4038-4960-8273-E2D1A48B8B1D}" name="Riesgo ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{C59E246A-73E5-4D4B-8118-3EC39715F667}" name="Descripción (CTC)" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{905ACF41-B343-4F2B-AC21-175172158836}" name="Categoría del riesgo" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{941A7795-F4B0-4017-B5A4-50F820C621F6}" name="Fecha" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{2B1A0CE7-58E0-4E2B-83AB-F1F8F424AAA6}" name="Costo de ocurrencia(C)" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{49018337-BE42-472E-B956-1D85E3767C39}" name="Probabilidad de ocurrencia(P)" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{91D5570D-A982-4A04-9AFF-000C99C9317E}" name="Exposición al Riesgo (ER)" dataDxfId="6">
+    <tableColumn id="1" xr3:uid="{4304278C-4038-4960-8273-E2D1A48B8B1D}" name="Riesgo ID" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{C59E246A-73E5-4D4B-8118-3EC39715F667}" name="Descripción (CTC)" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{905ACF41-B343-4F2B-AC21-175172158836}" name="Categoría del riesgo" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{941A7795-F4B0-4017-B5A4-50F820C621F6}" name="Fecha" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{2B1A0CE7-58E0-4E2B-83AB-F1F8F424AAA6}" name="Costo de ocurrencia(C)" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{49018337-BE42-472E-B956-1D85E3767C39}" name="Probabilidad de ocurrencia(P)" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{91D5570D-A982-4A04-9AFF-000C99C9317E}" name="Exposición al Riesgo (ER)" dataDxfId="5">
       <calculatedColumnFormula>E4*F4</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{E63596DF-75AC-4922-A4D8-24F3001C17A5}" name="Impacto" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{E63596DF-75AC-4922-A4D8-24F3001C17A5}" name="Impacto" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4615EB50-CCD4-4C8E-9CED-D0FC50DEA829}" name="Tabla2" displayName="Tabla2" ref="I3:K12" totalsRowShown="0" headerRowBorderDxfId="2" tableBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{4615EB50-CCD4-4C8E-9CED-D0FC50DEA829}" name="Tabla2" displayName="Tabla2" ref="I3:K12" totalsRowShown="0" headerRowBorderDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="I3:K12" xr:uid="{4615EB50-CCD4-4C8E-9CED-D0FC50DEA829}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{FA4D8F4A-4608-4D93-9FCC-A801DA76568E}" name="Contexto" dataDxfId="1"/>
@@ -1104,39 +1089,39 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+    </row>
+    <row r="2" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-    </row>
-    <row r="2" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="J2" s="38"/>
-      <c r="K2" s="39"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="33"/>
     </row>
     <row r="3" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="23" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="15" t="s">
@@ -1145,37 +1130,37 @@
       <c r="C3" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="26" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="27" t="s">
         <v>6</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="198" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>15</v>
@@ -1190,31 +1175,31 @@
         <v>0.1</v>
       </c>
       <c r="G4" s="11">
-        <f>E4*F4</f>
+        <f t="shared" ref="G4:G12" si="0">E4*F4</f>
         <v>20000</v>
       </c>
-      <c r="H4" s="25" t="s">
+      <c r="H4" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="K4" s="20" t="s">
-        <v>51</v>
-      </c>
     </row>
     <row r="5" spans="1:14" ht="156" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5" s="10" t="s">
         <v>30</v>
@@ -1226,28 +1211,28 @@
         <v>0.1</v>
       </c>
       <c r="G5" s="11">
-        <f>E5*F5</f>
+        <f t="shared" si="0"/>
         <v>20000</v>
       </c>
-      <c r="H5" s="25" t="s">
+      <c r="H5" s="9" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J5" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="J5" s="19" t="s">
-        <v>47</v>
-      </c>
       <c r="K5" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="252" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>8</v>
@@ -1262,28 +1247,28 @@
         <v>0.6</v>
       </c>
       <c r="G6" s="11">
-        <f>E6*F6</f>
+        <f t="shared" si="0"/>
         <v>18000</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="357" x14ac:dyDescent="0.2">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="21" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>15</v>
@@ -1298,32 +1283,32 @@
         <v>0.6</v>
       </c>
       <c r="G7" s="11">
-        <f>E7*F7</f>
+        <f t="shared" si="0"/>
         <v>15000</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N7" s="18"/>
     </row>
     <row r="8" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
-      <c r="A8" s="26" t="s">
-        <v>44</v>
+      <c r="A8" s="21" t="s">
+        <v>43</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D8" s="10">
         <v>45728</v>
@@ -1335,21 +1320,21 @@
         <v>0.15</v>
       </c>
       <c r="G8" s="11">
-        <f>E8*F8</f>
+        <f t="shared" si="0"/>
         <v>10500</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="14"/>
       <c r="K8" s="16"/>
     </row>
     <row r="9" spans="1:14" ht="82.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="22" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>24</v>
@@ -1364,17 +1349,17 @@
         <v>0.05</v>
       </c>
       <c r="G9" s="11">
-        <f>E9*F9</f>
+        <f t="shared" si="0"/>
         <v>10000</v>
       </c>
-      <c r="H9" s="25" t="s">
+      <c r="H9" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="14"/>
       <c r="K9" s="16"/>
     </row>
     <row r="10" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="13" t="s">
@@ -1393,17 +1378,17 @@
         <v>0.01</v>
       </c>
       <c r="G10" s="11">
-        <f>E10*F10</f>
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="H10" s="25" t="s">
+      <c r="H10" s="9" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="14"/>
       <c r="K10" s="16"/>
     </row>
     <row r="11" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -1422,47 +1407,46 @@
         <v>0.01</v>
       </c>
       <c r="G11" s="11">
-        <f>E11*F11</f>
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="H11" s="25" t="s">
+      <c r="H11" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I11" s="14"/>
       <c r="K11" s="16"/>
     </row>
     <row r="12" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="25" t="s">
+      <c r="A12" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="25" t="s">
+      <c r="B12" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="34">
+      <c r="D12" s="10">
         <v>46023</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="11">
         <v>35000</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="12">
         <v>0.01</v>
       </c>
-      <c r="G12" s="35">
-        <f>E12*F12</f>
+      <c r="G12" s="11">
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="14"/>
-      <c r="J12" s="40"/>
       <c r="K12" s="16"/>
     </row>
     <row r="13" spans="1:14" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="D13" s="1"/>
+      <c r="D13" s="35"/>
       <c r="E13" s="2"/>
       <c r="F13" s="3"/>
     </row>
@@ -6407,12 +6391,11 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="C4:C12" xr:uid="{9969F3A2-8AC9-4A35-95E5-292F914BB602}">
       <formula1>"Presupuestal,Proyecto,Técnico,Administrativo,Mercado,Tamaño del Producto,Ventas,Presupuestal,Estrategia"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="K5" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
-    <dataValidation allowBlank="1" showErrorMessage="1" sqref="J4 K3" xr:uid="{2CBE015B-5C5A-4A99-B624-9657E53B9E36}"/>
+    <dataValidation allowBlank="1" showErrorMessage="1" sqref="K5 J4 K3" xr:uid="{00000000-0002-0000-0000-000001000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
